--- a/outputs/part_c/summaries/part_c_surface_cover_summary.xlsx
+++ b/outputs/part_c/summaries/part_c_surface_cover_summary.xlsx
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>57.133179</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57.133179</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>57.133179</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57.133179</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57.133179</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>57.133179</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>57.133179</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57.133179</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>57.133179</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>57.133179</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47.137451</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47.137451</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>47.137451</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>47.137451</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>47.137451</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>47.137451</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>47.137451</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>47.137451</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>47.137451</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>47.137451</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>42.356567</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>42.356567</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>42.356567</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>42.356567</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>42.356567</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>42.356567</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>42.356567</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>42.356567</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>42.356567</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>42.356567</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37.871399</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>37.871399</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>37.871399</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>37.871399</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>37.871399</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>37.871399</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>37.871399</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>37.871399</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>37.871399</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>37.871399</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>27.702332</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>27.702332</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>27.702332</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>27.702332</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>27.702332</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>27.702332</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>27.702332</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>27.702332</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>27.702332</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>27.702332</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
